--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031955</v>
+        <v>130031962</v>
       </c>
       <c r="B5" t="n">
-        <v>92341</v>
+        <v>96257</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639065</v>
+        <v>638964</v>
       </c>
       <c r="R5" t="n">
-        <v>6540838</v>
+        <v>6540946</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B6" t="n">
-        <v>96257</v>
+        <v>92341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,35 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R6" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B5" t="n">
-        <v>96273</v>
+        <v>92357</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,35 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R5" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1100,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031955</v>
+        <v>130031962</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>96273</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,30 +1106,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639065</v>
+        <v>638964</v>
       </c>
       <c r="R6" t="n">
-        <v>6540838</v>
+        <v>6540946</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031955</v>
+        <v>130031962</v>
       </c>
       <c r="B5" t="n">
-        <v>92357</v>
+        <v>96273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639065</v>
+        <v>638964</v>
       </c>
       <c r="R5" t="n">
-        <v>6540838</v>
+        <v>6540946</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B6" t="n">
-        <v>96273</v>
+        <v>92357</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,35 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R6" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130031958</v>
       </c>
       <c r="B2" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>130031960</v>
       </c>
       <c r="B4" t="n">
-        <v>96273</v>
+        <v>96275</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>130031962</v>
       </c>
       <c r="B5" t="n">
-        <v>96273</v>
+        <v>96275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130031955</v>
       </c>
       <c r="B6" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,46 +1205,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130031961</v>
+        <v>130031954</v>
       </c>
       <c r="B7" t="n">
-        <v>96273</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638975</v>
+        <v>639040</v>
       </c>
       <c r="R7" t="n">
-        <v>6540791</v>
+        <v>6540790</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,7 +1291,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,41 +1309,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130031954</v>
+        <v>130031961</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>96275</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639040</v>
+        <v>638975</v>
       </c>
       <c r="R8" t="n">
-        <v>6540790</v>
+        <v>6540791</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,6 +1400,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1422,7 +1422,7 @@
         <v>130031963</v>
       </c>
       <c r="B9" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130031958</v>
       </c>
       <c r="B2" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>130031959</v>
       </c>
       <c r="B3" t="n">
-        <v>43995</v>
+        <v>44080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>130031960</v>
       </c>
       <c r="B4" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B5" t="n">
-        <v>96275</v>
+        <v>92446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,35 +1001,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R5" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1100,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031955</v>
+        <v>130031962</v>
       </c>
       <c r="B6" t="n">
-        <v>92359</v>
+        <v>96362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,30 +1106,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>639065</v>
+        <v>638964</v>
       </c>
       <c r="R6" t="n">
-        <v>6540838</v>
+        <v>6540946</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1208,7 +1208,7 @@
         <v>130031954</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>130031961</v>
       </c>
       <c r="B8" t="n">
-        <v>96275</v>
+        <v>96362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>130031963</v>
       </c>
       <c r="B9" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031955</v>
+        <v>130031962</v>
       </c>
       <c r="B5" t="n">
-        <v>92446</v>
+        <v>96362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,30 +1001,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639065</v>
+        <v>638964</v>
       </c>
       <c r="R5" t="n">
-        <v>6540838</v>
+        <v>6540946</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1095,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B6" t="n">
-        <v>96362</v>
+        <v>92446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,35 +1111,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R6" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,41 +1205,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130031954</v>
+        <v>130031961</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>96362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1247,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639040</v>
+        <v>638975</v>
       </c>
       <c r="R7" t="n">
-        <v>6540790</v>
+        <v>6540791</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1309,46 +1315,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130031961</v>
+        <v>130031954</v>
       </c>
       <c r="B8" t="n">
-        <v>96362</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638975</v>
+        <v>639040</v>
       </c>
       <c r="R8" t="n">
-        <v>6540791</v>
+        <v>6540790</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1400,7 +1401,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -1205,46 +1205,41 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130031961</v>
+        <v>130031954</v>
       </c>
       <c r="B7" t="n">
-        <v>96362</v>
+        <v>91728</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1252,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638975</v>
+        <v>639040</v>
       </c>
       <c r="R7" t="n">
-        <v>6540791</v>
+        <v>6540790</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1296,7 +1291,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1315,41 +1309,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130031954</v>
+        <v>130031961</v>
       </c>
       <c r="B8" t="n">
-        <v>91728</v>
+        <v>96362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1357,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>639040</v>
+        <v>638975</v>
       </c>
       <c r="R8" t="n">
-        <v>6540790</v>
+        <v>6540791</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,6 +1400,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -1205,41 +1205,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130031954</v>
+        <v>130031961</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>96362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1247,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639040</v>
+        <v>638975</v>
       </c>
       <c r="R7" t="n">
-        <v>6540790</v>
+        <v>6540791</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,6 +1296,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1309,46 +1315,41 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130031961</v>
+        <v>130031954</v>
       </c>
       <c r="B8" t="n">
-        <v>96362</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1356,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638975</v>
+        <v>639040</v>
       </c>
       <c r="R8" t="n">
-        <v>6540791</v>
+        <v>6540790</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1400,7 +1401,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130031958</v>
+        <v>130031960</v>
       </c>
       <c r="B2" t="n">
-        <v>105987</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Nytorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638969</v>
+        <v>638996</v>
       </c>
       <c r="R2" t="n">
-        <v>6540795</v>
+        <v>6540777</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -773,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130031959</v>
+        <v>130031961</v>
       </c>
       <c r="B3" t="n">
-        <v>44080</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -784,32 +796,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101735</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638935</v>
+        <v>638975</v>
       </c>
       <c r="R3" t="n">
-        <v>6540870</v>
+        <v>6540791</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -880,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130031960</v>
+        <v>130031962</v>
       </c>
       <c r="B4" t="n">
-        <v>96362</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,7 +925,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -927,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638996</v>
+        <v>638964</v>
       </c>
       <c r="R4" t="n">
-        <v>6540777</v>
+        <v>6540946</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -990,32 +1005,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130031955</v>
+        <v>130031954</v>
       </c>
       <c r="B5" t="n">
-        <v>92446</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>639065</v>
+        <v>639040</v>
       </c>
       <c r="R5" t="n">
-        <v>6540838</v>
+        <v>6540790</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1091,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130031962</v>
+        <v>130031955</v>
       </c>
       <c r="B6" t="n">
-        <v>96362</v>
+        <v>92632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,35 +1120,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>210</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1142,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638964</v>
+        <v>639065</v>
       </c>
       <c r="R6" t="n">
-        <v>6540946</v>
+        <v>6540838</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,41 +1214,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130031954</v>
+        <v>130031959</v>
       </c>
       <c r="B7" t="n">
-        <v>91728</v>
+        <v>44177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1247,10 +1258,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>639040</v>
+        <v>638935</v>
       </c>
       <c r="R7" t="n">
-        <v>6540790</v>
+        <v>6540870</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1291,6 +1302,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1309,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130031961</v>
+        <v>130031958</v>
       </c>
       <c r="B8" t="n">
-        <v>96362</v>
+        <v>106243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1320,46 +1332,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nytorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638975</v>
+        <v>638969</v>
       </c>
       <c r="R8" t="n">
-        <v>6540791</v>
+        <v>6540795</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1422,7 +1422,7 @@
         <v>130031963</v>
       </c>
       <c r="B9" t="n">
-        <v>101109</v>
+        <v>101325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 57411-2025 artfynd.xlsx
+++ b/artfynd/A 57411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031960</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031961</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031962</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031954</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031955</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031959</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031958</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1513,8 +1553,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130031963</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>